--- a/prix/levis.xlsx
+++ b/prix/levis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F97A5AC-91B7-4767-8AD5-1FBD98AF72EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE880A0-3710-42C2-BE34-5CD27B4CF849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -1003,7 +1003,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1029,9 +1029,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1407,7 +1404,7 @@
       <c r="F1" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="G1" s="11"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -1419,16 +1416,16 @@
       <c r="C2" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="11">
         <v>45</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="13">
-        <v>7</v>
-      </c>
-      <c r="G2" s="11"/>
+      <c r="F2" s="12">
+        <v>3</v>
+      </c>
+      <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -1440,16 +1437,16 @@
       <c r="C3" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="11">
         <v>45</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="13">
-        <v>7</v>
-      </c>
-      <c r="G3" s="11"/>
+      <c r="F3" s="12">
+        <v>5</v>
+      </c>
+      <c r="G3" s="10"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -1461,16 +1458,16 @@
       <c r="C4" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <v>94</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="13">
-        <v>6</v>
-      </c>
-      <c r="G4" s="11"/>
+      <c r="F4" s="12">
+        <v>3</v>
+      </c>
+      <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -1482,16 +1479,16 @@
       <c r="C5" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11">
         <v>94</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="13">
-        <v>3</v>
-      </c>
-      <c r="G5" s="11"/>
+      <c r="F5" s="12">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -1503,16 +1500,16 @@
       <c r="C6" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="11">
         <v>175</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="13">
-        <v>6</v>
-      </c>
-      <c r="G6" s="11"/>
+      <c r="F6" s="12">
+        <v>3</v>
+      </c>
+      <c r="G6" s="10"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -1524,16 +1521,16 @@
       <c r="C7" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <v>175</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
         <v>1</v>
       </c>
-      <c r="G7" s="11"/>
+      <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -1545,16 +1542,16 @@
       <c r="C8" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <v>175</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="13">
-        <v>3</v>
-      </c>
-      <c r="G8" s="11"/>
+      <c r="F8" s="12">
+        <v>4</v>
+      </c>
+      <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -1566,16 +1563,16 @@
       <c r="C9" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D9" s="12">
-        <v>47.25</v>
+      <c r="D9" s="11">
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="13">
-        <v>0</v>
-      </c>
-      <c r="G9" s="11"/>
+      <c r="F9" s="12">
+        <v>6</v>
+      </c>
+      <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -1587,16 +1584,16 @@
       <c r="C10" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D10" s="12">
-        <v>45</v>
+      <c r="D10" s="11">
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="13">
-        <v>3</v>
-      </c>
-      <c r="G10" s="11"/>
+      <c r="F10" s="12">
+        <v>6</v>
+      </c>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -1608,16 +1605,16 @@
       <c r="C11" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D11" s="12">
-        <v>45</v>
+      <c r="D11" s="11">
+        <v>63</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="13">
-        <v>0</v>
-      </c>
-      <c r="G11" s="11"/>
+      <c r="F11" s="12">
+        <v>4</v>
+      </c>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -1629,16 +1626,16 @@
       <c r="C12" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D12" s="12">
-        <v>45</v>
+      <c r="D12" s="11">
+        <v>63</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="12">
         <v>4</v>
       </c>
-      <c r="G12" s="11"/>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -1650,16 +1647,16 @@
       <c r="C13" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D13" s="12">
-        <v>94</v>
+      <c r="D13" s="11">
+        <v>118</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="13">
-        <v>2</v>
-      </c>
-      <c r="G13" s="11"/>
+      <c r="F13" s="12">
+        <v>4</v>
+      </c>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1671,16 +1668,16 @@
       <c r="C14" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D14" s="12">
-        <v>94</v>
+      <c r="D14" s="11">
+        <v>118</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="13">
-        <v>0</v>
-      </c>
-      <c r="G14" s="11"/>
+      <c r="F14" s="12">
+        <v>4</v>
+      </c>
+      <c r="G14" s="10"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -1692,16 +1689,16 @@
       <c r="C15" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D15" s="12">
-        <v>94</v>
+      <c r="D15" s="11">
+        <v>47.25</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="13">
-        <v>2</v>
-      </c>
-      <c r="G15" s="11"/>
+      <c r="F15" s="12">
+        <v>0</v>
+      </c>
+      <c r="G15" s="10"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1713,16 +1710,16 @@
       <c r="C16" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D16" s="12">
-        <v>175</v>
+      <c r="D16" s="11">
+        <v>45</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="13">
-        <v>3</v>
-      </c>
-      <c r="G16" s="11"/>
+      <c r="F16" s="12">
+        <v>0</v>
+      </c>
+      <c r="G16" s="10"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -1734,16 +1731,16 @@
       <c r="C17" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D17" s="12">
-        <v>175</v>
+      <c r="D17" s="11">
+        <v>45</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="12">
         <v>0</v>
       </c>
-      <c r="G17" s="11"/>
+      <c r="G17" s="10"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -1755,16 +1752,16 @@
       <c r="C18" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D18" s="12">
-        <v>175</v>
+      <c r="D18" s="11">
+        <v>45</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="13">
-        <v>6</v>
-      </c>
-      <c r="G18" s="11"/>
+      <c r="F18" s="12">
+        <v>4</v>
+      </c>
+      <c r="G18" s="10"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B19" s="9" t="s">
@@ -1773,16 +1770,16 @@
       <c r="C19" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D19" s="12">
-        <v>46.95</v>
+      <c r="D19" s="11">
+        <v>94</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="12">
         <v>0</v>
       </c>
-      <c r="G19" s="11"/>
+      <c r="G19" s="10"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -1794,16 +1791,16 @@
       <c r="C20" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D20" s="12">
-        <v>32</v>
+      <c r="D20" s="11">
+        <v>94</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="13">
-        <v>1</v>
-      </c>
-      <c r="G20" s="11"/>
+      <c r="F20" s="12">
+        <v>0</v>
+      </c>
+      <c r="G20" s="10"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -1815,16 +1812,16 @@
       <c r="C21" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D21" s="12">
-        <v>32</v>
+      <c r="D21" s="11">
+        <v>94</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="13">
-        <v>3</v>
-      </c>
-      <c r="G21" s="11"/>
+      <c r="F21" s="12">
+        <v>2</v>
+      </c>
+      <c r="G21" s="10"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -1836,16 +1833,16 @@
       <c r="C22" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D22" s="12">
-        <v>32</v>
+      <c r="D22" s="11">
+        <v>175</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="13">
-        <v>3</v>
-      </c>
-      <c r="G22" s="11"/>
+      <c r="F22" s="12">
+        <v>2</v>
+      </c>
+      <c r="G22" s="10"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -1857,16 +1854,16 @@
       <c r="C23" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D23" s="12">
-        <v>58</v>
+      <c r="D23" s="11">
+        <v>175</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="12">
         <v>0</v>
       </c>
-      <c r="G23" s="11"/>
+      <c r="G23" s="10"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -1878,16 +1875,16 @@
       <c r="C24" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D24" s="12">
-        <v>58</v>
+      <c r="D24" s="11">
+        <v>175</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F24" s="13">
-        <v>3</v>
-      </c>
-      <c r="G24" s="11"/>
+      <c r="F24" s="12">
+        <v>5</v>
+      </c>
+      <c r="G24" s="10"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -1899,16 +1896,16 @@
       <c r="C25" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D25" s="12">
-        <v>58</v>
+      <c r="D25" s="11">
+        <v>46.95</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="13">
-        <v>2</v>
-      </c>
-      <c r="G25" s="11"/>
+      <c r="F25" s="12">
+        <v>0</v>
+      </c>
+      <c r="G25" s="10"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -1920,16 +1917,16 @@
       <c r="C26" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D26" s="12">
-        <v>145</v>
+      <c r="D26" s="11">
+        <v>32</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="12">
         <v>1</v>
       </c>
-      <c r="G26" s="11"/>
+      <c r="G26" s="10"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
@@ -1941,16 +1938,16 @@
       <c r="C27" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D27" s="12">
-        <v>135.5</v>
+      <c r="D27" s="11">
+        <v>32</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="12">
         <v>3</v>
       </c>
-      <c r="G27" s="11"/>
+      <c r="G27" s="10"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -1962,16 +1959,16 @@
       <c r="C28" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D28" s="12">
-        <v>135.5</v>
+      <c r="D28" s="11">
+        <v>32</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="13">
-        <v>7</v>
-      </c>
-      <c r="G28" s="11"/>
+      <c r="F28" s="12">
+        <v>3</v>
+      </c>
+      <c r="G28" s="10"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -1983,16 +1980,16 @@
       <c r="C29" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D29" s="12">
-        <v>37</v>
+      <c r="D29" s="11">
+        <v>58</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F29" s="13">
-        <v>5</v>
-      </c>
-      <c r="G29" s="11"/>
+      <c r="F29" s="12">
+        <v>0</v>
+      </c>
+      <c r="G29" s="10"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -2004,16 +2001,16 @@
       <c r="C30" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D30" s="12">
-        <v>36</v>
+      <c r="D30" s="11">
+        <v>58</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="13">
-        <v>6</v>
-      </c>
-      <c r="G30" s="11"/>
+      <c r="F30" s="12">
+        <v>3</v>
+      </c>
+      <c r="G30" s="10"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -2025,16 +2022,16 @@
       <c r="C31" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D31" s="12">
-        <v>37</v>
+      <c r="D31" s="11">
+        <v>58</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="13">
-        <v>12</v>
-      </c>
-      <c r="G31" s="11"/>
+      <c r="F31" s="12">
+        <v>2</v>
+      </c>
+      <c r="G31" s="10"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -2046,16 +2043,16 @@
       <c r="C32" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D32" s="12">
-        <v>65</v>
+      <c r="D32" s="11">
+        <v>145</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="13">
-        <v>11</v>
-      </c>
-      <c r="G32" s="11"/>
+      <c r="F32" s="12">
+        <v>0</v>
+      </c>
+      <c r="G32" s="10"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -2067,16 +2064,16 @@
       <c r="C33" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D33" s="12">
-        <v>65</v>
+      <c r="D33" s="11">
+        <v>135.5</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F33" s="13">
-        <v>1</v>
-      </c>
-      <c r="G33" s="11"/>
+      <c r="F33" s="12">
+        <v>3</v>
+      </c>
+      <c r="G33" s="10"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
@@ -2088,16 +2085,16 @@
       <c r="C34" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D34" s="12">
-        <v>65</v>
+      <c r="D34" s="11">
+        <v>135.5</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="13">
-        <v>8</v>
-      </c>
-      <c r="G34" s="11"/>
+      <c r="F34" s="12">
+        <v>7</v>
+      </c>
+      <c r="G34" s="10"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
@@ -2109,16 +2106,16 @@
       <c r="C35" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D35" s="12">
-        <v>150</v>
+      <c r="D35" s="11">
+        <v>37</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F35" s="13">
-        <v>4</v>
-      </c>
-      <c r="G35" s="11"/>
+      <c r="F35" s="12">
+        <v>6</v>
+      </c>
+      <c r="G35" s="10"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
@@ -2130,16 +2127,16 @@
       <c r="C36" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D36" s="12">
-        <v>150</v>
+      <c r="D36" s="11">
+        <v>36</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F36" s="13">
-        <v>0</v>
-      </c>
-      <c r="G36" s="11"/>
+      <c r="F36" s="12">
+        <v>5</v>
+      </c>
+      <c r="G36" s="10"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
@@ -2151,16 +2148,16 @@
       <c r="C37" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D37" s="12">
-        <v>150</v>
+      <c r="D37" s="11">
+        <v>37</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="13">
-        <v>4</v>
-      </c>
-      <c r="G37" s="11"/>
+      <c r="F37" s="12">
+        <v>11</v>
+      </c>
+      <c r="G37" s="10"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
@@ -2172,16 +2169,16 @@
       <c r="C38" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D38" s="12">
-        <v>36</v>
+      <c r="D38" s="11">
+        <v>65</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38" s="12">
         <v>7</v>
       </c>
-      <c r="G38" s="11"/>
+      <c r="G38" s="10"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
@@ -2193,16 +2190,16 @@
       <c r="C39" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D39" s="12">
-        <v>36</v>
+      <c r="D39" s="11">
+        <v>65</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="13">
-        <v>8</v>
-      </c>
-      <c r="G39" s="11"/>
+      <c r="F39" s="12">
+        <v>1</v>
+      </c>
+      <c r="G39" s="10"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -2214,16 +2211,16 @@
       <c r="C40" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D40" s="12">
-        <v>36</v>
+      <c r="D40" s="11">
+        <v>65</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F40" s="13">
-        <v>10</v>
-      </c>
-      <c r="G40" s="11"/>
+      <c r="F40" s="12">
+        <v>5</v>
+      </c>
+      <c r="G40" s="10"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
@@ -2235,16 +2232,16 @@
       <c r="C41" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D41" s="12">
-        <v>65</v>
+      <c r="D41" s="11">
+        <v>150</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F41" s="13">
-        <v>4</v>
-      </c>
-      <c r="G41" s="11"/>
+      <c r="F41" s="12">
+        <v>3</v>
+      </c>
+      <c r="G41" s="10"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
@@ -2256,16 +2253,16 @@
       <c r="C42" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D42" s="12">
-        <v>65</v>
+      <c r="D42" s="11">
+        <v>150</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F42" s="13">
-        <v>3</v>
-      </c>
-      <c r="G42" s="11"/>
+      <c r="F42" s="12">
+        <v>0</v>
+      </c>
+      <c r="G42" s="10"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
@@ -2277,16 +2274,16 @@
       <c r="C43" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D43" s="12">
-        <v>65</v>
+      <c r="D43" s="11">
+        <v>150</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F43" s="13">
-        <v>2</v>
-      </c>
-      <c r="G43" s="11"/>
+      <c r="F43" s="12">
+        <v>4</v>
+      </c>
+      <c r="G43" s="10"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
@@ -2298,16 +2295,16 @@
       <c r="C44" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D44" s="12">
-        <v>145</v>
+      <c r="D44" s="11">
+        <v>36</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F44" s="13">
-        <v>5</v>
-      </c>
-      <c r="G44" s="11"/>
+      <c r="F44" s="12">
+        <v>7</v>
+      </c>
+      <c r="G44" s="10"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -2319,16 +2316,16 @@
       <c r="C45" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D45" s="12">
-        <v>145</v>
+      <c r="D45" s="11">
+        <v>36</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F45" s="13">
-        <v>0</v>
-      </c>
-      <c r="G45" s="11"/>
+      <c r="F45" s="12">
+        <v>8</v>
+      </c>
+      <c r="G45" s="10"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
@@ -2340,16 +2337,16 @@
       <c r="C46" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D46" s="12">
-        <v>145</v>
+      <c r="D46" s="11">
+        <v>36</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F46" s="13">
-        <v>1</v>
-      </c>
-      <c r="G46" s="11"/>
+      <c r="F46" s="12">
+        <v>8</v>
+      </c>
+      <c r="G46" s="10"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
@@ -2361,16 +2358,16 @@
       <c r="C47" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D47" s="12">
-        <v>29.8</v>
+      <c r="D47" s="11">
+        <v>65</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F47" s="13">
-        <v>0</v>
-      </c>
-      <c r="G47" s="11"/>
+      <c r="F47" s="12">
+        <v>3</v>
+      </c>
+      <c r="G47" s="10"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
@@ -2382,16 +2379,16 @@
       <c r="C48" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D48" s="12">
-        <v>29.8</v>
+      <c r="D48" s="11">
+        <v>65</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F48" s="13">
-        <v>0</v>
-      </c>
-      <c r="G48" s="11"/>
+      <c r="F48" s="12">
+        <v>3</v>
+      </c>
+      <c r="G48" s="10"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
@@ -2403,16 +2400,16 @@
       <c r="C49" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D49" s="12">
-        <v>29.8</v>
+      <c r="D49" s="11">
+        <v>65</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F49" s="13">
-        <v>0</v>
-      </c>
-      <c r="G49" s="11"/>
+      <c r="F49" s="12">
+        <v>1</v>
+      </c>
+      <c r="G49" s="10"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
@@ -2424,16 +2421,16 @@
       <c r="C50" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D50" s="12">
-        <v>69.150000000000006</v>
+      <c r="D50" s="11">
+        <v>145</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F50" s="13">
-        <v>0</v>
-      </c>
-      <c r="G50" s="11"/>
+      <c r="F50" s="12">
+        <v>5</v>
+      </c>
+      <c r="G50" s="10"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
@@ -2445,16 +2442,16 @@
       <c r="C51" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D51" s="12">
-        <v>69.150000000000006</v>
+      <c r="D51" s="11">
+        <v>150</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F51" s="13">
+      <c r="F51" s="12">
         <v>0</v>
       </c>
-      <c r="G51" s="11"/>
+      <c r="G51" s="10"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
@@ -2466,16 +2463,16 @@
       <c r="C52" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D52" s="12">
-        <v>69.150000000000006</v>
+      <c r="D52" s="11">
+        <v>150</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F52" s="13">
-        <v>0</v>
-      </c>
-      <c r="G52" s="11"/>
+      <c r="F52" s="12">
+        <v>2</v>
+      </c>
+      <c r="G52" s="10"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
@@ -2487,16 +2484,16 @@
       <c r="C53" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D53" s="12">
-        <v>150.49</v>
+      <c r="D53" s="11">
+        <v>29.8</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F53" s="13">
+      <c r="F53" s="12">
         <v>0</v>
       </c>
-      <c r="G53" s="11"/>
+      <c r="G53" s="10"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
@@ -2508,16 +2505,16 @@
       <c r="C54" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D54" s="12">
-        <v>150.49</v>
+      <c r="D54" s="11">
+        <v>29.8</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F54" s="13">
+      <c r="F54" s="12">
         <v>0</v>
       </c>
-      <c r="G54" s="11"/>
+      <c r="G54" s="10"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
@@ -2529,16 +2526,16 @@
       <c r="C55" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D55" s="12">
-        <v>150.49</v>
+      <c r="D55" s="11">
+        <v>29.8</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F55" s="13">
-        <v>-2</v>
-      </c>
-      <c r="G55" s="11"/>
+      <c r="F55" s="12">
+        <v>0</v>
+      </c>
+      <c r="G55" s="10"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
@@ -2550,16 +2547,16 @@
       <c r="C56" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D56" s="12">
-        <v>35</v>
+      <c r="D56" s="11">
+        <v>69.150000000000006</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F56" s="13">
-        <v>4</v>
-      </c>
-      <c r="G56" s="11"/>
+      <c r="F56" s="12">
+        <v>0</v>
+      </c>
+      <c r="G56" s="10"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
@@ -2571,16 +2568,16 @@
       <c r="C57" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D57" s="12">
-        <v>35</v>
+      <c r="D57" s="11">
+        <v>69.150000000000006</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F57" s="13">
-        <v>5</v>
-      </c>
-      <c r="G57" s="11"/>
+      <c r="F57" s="12">
+        <v>0</v>
+      </c>
+      <c r="G57" s="10"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
@@ -2592,16 +2589,16 @@
       <c r="C58" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D58" s="12">
-        <v>35</v>
+      <c r="D58" s="11">
+        <v>69.150000000000006</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F58" s="13">
-        <v>5</v>
-      </c>
-      <c r="G58" s="11"/>
+      <c r="F58" s="12">
+        <v>0</v>
+      </c>
+      <c r="G58" s="10"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
@@ -2613,16 +2610,16 @@
       <c r="C59" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D59" s="12">
-        <v>151</v>
+      <c r="D59" s="11">
+        <v>150.49</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F59" s="13">
-        <v>2</v>
-      </c>
-      <c r="G59" s="11"/>
+      <c r="F59" s="12">
+        <v>0</v>
+      </c>
+      <c r="G59" s="10"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
@@ -2634,16 +2631,16 @@
       <c r="C60" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D60" s="12">
-        <v>151</v>
+      <c r="D60" s="11">
+        <v>150.49</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F60" s="13">
+      <c r="F60" s="12">
         <v>0</v>
       </c>
-      <c r="G60" s="11"/>
+      <c r="G60" s="10"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
@@ -2655,16 +2652,16 @@
       <c r="C61" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D61" s="12">
-        <v>151</v>
+      <c r="D61" s="11">
+        <v>150.49</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F61" s="13">
-        <v>3</v>
-      </c>
-      <c r="G61" s="11"/>
+      <c r="F61" s="12">
+        <v>-2</v>
+      </c>
+      <c r="G61" s="10"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
@@ -2676,16 +2673,16 @@
       <c r="C62" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D62" s="12">
-        <v>37</v>
+      <c r="D62" s="11">
+        <v>48</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F62" s="13">
-        <v>5</v>
-      </c>
-      <c r="G62" s="11"/>
+      <c r="F62" s="12">
+        <v>6</v>
+      </c>
+      <c r="G62" s="10"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
@@ -2697,16 +2694,16 @@
       <c r="C63" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D63" s="12">
-        <v>37</v>
+      <c r="D63" s="11">
+        <v>48</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="F63" s="13">
+      <c r="F63" s="12">
         <v>6</v>
       </c>
-      <c r="G63" s="11"/>
+      <c r="G63" s="10"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
@@ -2718,16 +2715,16 @@
       <c r="C64" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D64" s="12">
-        <v>37</v>
+      <c r="D64" s="11">
+        <v>111</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F64" s="13">
-        <v>0</v>
-      </c>
-      <c r="G64" s="11"/>
+      <c r="F64" s="12">
+        <v>2</v>
+      </c>
+      <c r="G64" s="10"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
@@ -2739,16 +2736,16 @@
       <c r="C65" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D65" s="12">
-        <v>42.300000000000004</v>
+      <c r="D65" s="11">
+        <v>111</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F65" s="13">
-        <v>0</v>
-      </c>
-      <c r="G65" s="11"/>
+      <c r="F65" s="12">
+        <v>2</v>
+      </c>
+      <c r="G65" s="10"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
@@ -2760,16 +2757,16 @@
       <c r="C66" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D66" s="12">
-        <v>42.300000000000004</v>
+      <c r="D66" s="11">
+        <v>35</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F66" s="13">
-        <v>3</v>
-      </c>
-      <c r="G66" s="11"/>
+      <c r="F66" s="12">
+        <v>4</v>
+      </c>
+      <c r="G66" s="10"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
@@ -2781,16 +2778,16 @@
       <c r="C67" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D67" s="12">
-        <v>42.300000000000004</v>
+      <c r="D67" s="11">
+        <v>35</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F67" s="13">
-        <v>3</v>
-      </c>
-      <c r="G67" s="11"/>
+      <c r="F67" s="12">
+        <v>5</v>
+      </c>
+      <c r="G67" s="10"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
@@ -2802,16 +2799,16 @@
       <c r="C68" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D68" s="12">
-        <v>109.49000000000001</v>
+      <c r="D68" s="11">
+        <v>35</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F68" s="13">
-        <v>1</v>
-      </c>
-      <c r="G68" s="11"/>
+      <c r="F68" s="12">
+        <v>5</v>
+      </c>
+      <c r="G68" s="10"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
@@ -2823,16 +2820,16 @@
       <c r="C69" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D69" s="12">
-        <v>96.850000000000009</v>
+      <c r="D69" s="11">
+        <v>151</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F69" s="13">
+      <c r="F69" s="12">
         <v>2</v>
       </c>
-      <c r="G69" s="11"/>
+      <c r="G69" s="10"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
@@ -2844,16 +2841,16 @@
       <c r="C70" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D70" s="12">
-        <v>96.850000000000009</v>
+      <c r="D70" s="11">
+        <v>151</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="F70" s="13">
-        <v>2</v>
-      </c>
-      <c r="G70" s="11"/>
+      <c r="F70" s="12">
+        <v>0</v>
+      </c>
+      <c r="G70" s="10"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
@@ -2865,16 +2862,16 @@
       <c r="C71" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D71" s="12">
-        <v>37</v>
+      <c r="D71" s="11">
+        <v>151</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="F71" s="13">
-        <v>-3</v>
-      </c>
-      <c r="G71" s="11"/>
+      <c r="F71" s="12">
+        <v>3</v>
+      </c>
+      <c r="G71" s="10"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
@@ -2886,16 +2883,16 @@
       <c r="C72" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D72" s="12">
-        <v>34</v>
+      <c r="D72" s="11">
+        <v>37</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F72" s="13">
-        <v>1</v>
-      </c>
-      <c r="G72" s="11"/>
+      <c r="F72" s="12">
+        <v>5</v>
+      </c>
+      <c r="G72" s="10"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
@@ -2907,16 +2904,16 @@
       <c r="C73" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D73" s="12">
-        <v>34</v>
+      <c r="D73" s="11">
+        <v>37</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F73" s="13">
-        <v>2</v>
-      </c>
-      <c r="G73" s="11"/>
+      <c r="F73" s="12">
+        <v>6</v>
+      </c>
+      <c r="G73" s="10"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
@@ -2928,16 +2925,16 @@
       <c r="C74" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D74" s="12">
-        <v>46.5</v>
+      <c r="D74" s="11">
+        <v>37</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F74" s="13">
-        <v>1</v>
-      </c>
-      <c r="G74" s="11"/>
+      <c r="F74" s="12">
+        <v>0</v>
+      </c>
+      <c r="G74" s="10"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
@@ -2949,16 +2946,16 @@
       <c r="C75" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D75" s="12">
-        <v>60</v>
+      <c r="D75" s="11">
+        <v>42.300000000000004</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="F75" s="13">
-        <v>1</v>
-      </c>
-      <c r="G75" s="11"/>
+      <c r="F75" s="12">
+        <v>0</v>
+      </c>
+      <c r="G75" s="10"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
@@ -2970,16 +2967,16 @@
       <c r="C76" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D76" s="12">
-        <v>60</v>
+      <c r="D76" s="11">
+        <v>42.300000000000004</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="F76" s="13">
-        <v>7</v>
-      </c>
-      <c r="G76" s="11"/>
+      <c r="F76" s="12">
+        <v>3</v>
+      </c>
+      <c r="G76" s="10"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
@@ -2991,16 +2988,16 @@
       <c r="C77" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D77" s="12">
-        <v>136</v>
+      <c r="D77" s="11">
+        <v>42.300000000000004</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F77" s="13">
-        <v>1</v>
-      </c>
-      <c r="G77" s="11"/>
+      <c r="F77" s="12">
+        <v>3</v>
+      </c>
+      <c r="G77" s="10"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
@@ -3012,16 +3009,16 @@
       <c r="C78" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D78" s="12">
-        <v>136</v>
+      <c r="D78" s="11">
+        <v>109.49000000000001</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F78" s="13">
-        <v>2</v>
-      </c>
-      <c r="G78" s="11"/>
+      <c r="F78" s="12">
+        <v>1</v>
+      </c>
+      <c r="G78" s="10"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
@@ -3033,16 +3030,16 @@
       <c r="C79" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D79" s="12">
-        <v>136</v>
+      <c r="D79" s="11">
+        <v>96.850000000000009</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F79" s="13">
-        <v>-1</v>
-      </c>
-      <c r="G79" s="11"/>
+      <c r="F79" s="12">
+        <v>2</v>
+      </c>
+      <c r="G79" s="10"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
@@ -3054,16 +3051,16 @@
       <c r="C80" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D80" s="12">
-        <v>53</v>
+      <c r="D80" s="11">
+        <v>96.850000000000009</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F80" s="13">
-        <v>4</v>
-      </c>
-      <c r="G80" s="11"/>
+      <c r="F80" s="12">
+        <v>2</v>
+      </c>
+      <c r="G80" s="10"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
@@ -3075,16 +3072,16 @@
       <c r="C81" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D81" s="12">
-        <v>53</v>
+      <c r="D81" s="11">
+        <v>37</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="F81" s="13">
+      <c r="F81" s="12">
         <v>0</v>
       </c>
-      <c r="G81" s="11"/>
+      <c r="G81" s="10"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
@@ -3096,16 +3093,16 @@
       <c r="C82" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D82" s="12">
-        <v>123</v>
+      <c r="D82" s="11">
+        <v>34</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="F82" s="13">
-        <v>3</v>
-      </c>
-      <c r="G82" s="11"/>
+      <c r="F82" s="12">
+        <v>1</v>
+      </c>
+      <c r="G82" s="10"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
@@ -3117,16 +3114,16 @@
       <c r="C83" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D83" s="12">
-        <v>123</v>
+      <c r="D83" s="11">
+        <v>34</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F83" s="13">
-        <v>3</v>
-      </c>
-      <c r="G83" s="11"/>
+      <c r="F83" s="12">
+        <v>2</v>
+      </c>
+      <c r="G83" s="10"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B84" s="9" t="s">
@@ -3135,16 +3132,16 @@
       <c r="C84" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D84" s="12">
-        <v>36</v>
+      <c r="D84" s="11">
+        <v>46.5</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F84" s="13">
-        <v>3</v>
-      </c>
-      <c r="G84" s="11"/>
+      <c r="F84" s="12">
+        <v>0</v>
+      </c>
+      <c r="G84" s="10"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B85" s="9" t="s">
@@ -3153,16 +3150,16 @@
       <c r="C85" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D85" s="12">
-        <v>107</v>
+      <c r="D85" s="11">
+        <v>60</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="F85" s="13">
-        <v>3</v>
-      </c>
-      <c r="G85" s="11"/>
+      <c r="F85" s="12">
+        <v>1</v>
+      </c>
+      <c r="G85" s="10"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
@@ -3174,16 +3171,16 @@
       <c r="C86" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D86" s="12">
-        <v>39.5</v>
+      <c r="D86" s="11">
+        <v>60</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F86" s="13">
-        <v>2</v>
-      </c>
-      <c r="G86" s="11"/>
+      <c r="F86" s="12">
+        <v>7</v>
+      </c>
+      <c r="G86" s="10"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
@@ -3195,16 +3192,16 @@
       <c r="C87" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D87" s="12">
-        <v>39.5</v>
+      <c r="D87" s="11">
+        <v>145</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F87" s="13">
-        <v>2</v>
-      </c>
-      <c r="G87" s="11"/>
+      <c r="F87" s="12">
+        <v>3</v>
+      </c>
+      <c r="G87" s="10"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
@@ -3216,16 +3213,16 @@
       <c r="C88" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D88" s="12">
-        <v>90</v>
+      <c r="D88" s="11">
+        <v>145</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="F88" s="13">
+      <c r="F88" s="12">
         <v>2</v>
       </c>
-      <c r="G88" s="11"/>
+      <c r="G88" s="10"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
@@ -3237,16 +3234,16 @@
       <c r="C89" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D89" s="12">
-        <v>86</v>
+      <c r="D89" s="11">
+        <v>145</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F89" s="13">
-        <v>2</v>
-      </c>
-      <c r="G89" s="11"/>
+      <c r="F89" s="12">
+        <v>-1</v>
+      </c>
+      <c r="G89" s="10"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
@@ -3258,16 +3255,16 @@
       <c r="C90" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D90" s="12">
-        <v>130</v>
+      <c r="D90" s="11">
+        <v>53</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F90" s="13">
-        <v>1</v>
-      </c>
-      <c r="G90" s="11"/>
+      <c r="F90" s="12">
+        <v>4</v>
+      </c>
+      <c r="G90" s="10"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
@@ -3279,16 +3276,16 @@
       <c r="C91" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D91" s="12">
-        <v>130</v>
+      <c r="D91" s="11">
+        <v>53</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F91" s="13">
-        <v>2</v>
-      </c>
-      <c r="G91" s="11"/>
+      <c r="F91" s="12">
+        <v>0</v>
+      </c>
+      <c r="G91" s="10"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B92" s="9" t="s">
@@ -3297,16 +3294,16 @@
       <c r="C92" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D92" s="12">
-        <v>34.5</v>
+      <c r="D92" s="11">
+        <v>123</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F92" s="13">
-        <v>1</v>
-      </c>
-      <c r="G92" s="11"/>
+      <c r="F92" s="12">
+        <v>3</v>
+      </c>
+      <c r="G92" s="10"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B93" s="9" t="s">
@@ -3315,16 +3312,16 @@
       <c r="C93" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D93" s="12">
-        <v>71.5</v>
+      <c r="D93" s="11">
+        <v>123</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F93" s="13">
-        <v>0</v>
-      </c>
-      <c r="G93" s="11"/>
+      <c r="F93" s="12">
+        <v>3</v>
+      </c>
+      <c r="G93" s="10"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B94" s="9" t="s">
@@ -3333,16 +3330,16 @@
       <c r="C94" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D94" s="12">
-        <v>131.5</v>
+      <c r="D94" s="11">
+        <v>36</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="F94" s="13">
-        <v>0</v>
-      </c>
-      <c r="G94" s="11"/>
+      <c r="F94" s="12">
+        <v>3</v>
+      </c>
+      <c r="G94" s="10"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
@@ -3354,16 +3351,16 @@
       <c r="C95" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D95" s="12">
-        <v>36</v>
+      <c r="D95" s="11">
+        <v>107</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F95" s="13">
+      <c r="F95" s="12">
         <v>3</v>
       </c>
-      <c r="G95" s="11"/>
+      <c r="G95" s="10"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
@@ -3375,16 +3372,16 @@
       <c r="C96" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D96" s="12">
-        <v>36</v>
+      <c r="D96" s="11">
+        <v>39.5</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F96" s="13">
-        <v>1</v>
-      </c>
-      <c r="G96" s="11"/>
+      <c r="F96" s="12">
+        <v>0</v>
+      </c>
+      <c r="G96" s="10"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
@@ -3396,16 +3393,16 @@
       <c r="C97" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D97" s="12">
-        <v>78</v>
+      <c r="D97" s="11">
+        <v>39.5</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="F97" s="13">
-        <v>3</v>
-      </c>
-      <c r="G97" s="11"/>
+      <c r="F97" s="12">
+        <v>2</v>
+      </c>
+      <c r="G97" s="10"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
@@ -3417,16 +3414,16 @@
       <c r="C98" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D98" s="12">
-        <v>78</v>
+      <c r="D98" s="11">
+        <v>90</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="F98" s="13">
-        <v>2</v>
-      </c>
-      <c r="G98" s="11"/>
+      <c r="F98" s="12">
+        <v>1</v>
+      </c>
+      <c r="G98" s="10"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
@@ -3438,16 +3435,16 @@
       <c r="C99" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D99" s="12">
-        <v>150</v>
+      <c r="D99" s="11">
+        <v>86</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F99" s="13">
+      <c r="F99" s="12">
         <v>2</v>
       </c>
-      <c r="G99" s="11"/>
+      <c r="G99" s="10"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
@@ -3459,16 +3456,16 @@
       <c r="C100" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D100" s="12">
-        <v>150</v>
+      <c r="D100" s="11">
+        <v>130</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="F100" s="13">
-        <v>2</v>
-      </c>
-      <c r="G100" s="11"/>
+      <c r="F100" s="12">
+        <v>1</v>
+      </c>
+      <c r="G100" s="10"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B101" s="9" t="s">
@@ -3477,16 +3474,16 @@
       <c r="C101" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D101" s="12">
-        <v>71</v>
+      <c r="D101" s="11">
+        <v>130</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F101" s="13">
-        <v>0</v>
-      </c>
-      <c r="G101" s="11"/>
+      <c r="F101" s="12">
+        <v>2</v>
+      </c>
+      <c r="G101" s="10"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
@@ -3498,16 +3495,16 @@
       <c r="C102" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D102" s="12">
-        <v>35.5</v>
+      <c r="D102" s="11">
+        <v>37</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="F102" s="13">
-        <v>30</v>
-      </c>
-      <c r="G102" s="11"/>
+      <c r="F102" s="12">
+        <v>4</v>
+      </c>
+      <c r="G102" s="10"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
@@ -3519,16 +3516,16 @@
       <c r="C103" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D103" s="12">
-        <v>35.5</v>
+      <c r="D103" s="11">
+        <v>71.5</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F103" s="13">
+      <c r="F103" s="12">
         <v>0</v>
       </c>
-      <c r="G103" s="11"/>
+      <c r="G103" s="10"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
@@ -3540,16 +3537,16 @@
       <c r="C104" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D104" s="12">
-        <v>35.5</v>
+      <c r="D104" s="11">
+        <v>145</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="F104" s="13">
-        <v>4</v>
-      </c>
-      <c r="G104" s="11"/>
+      <c r="F104" s="12">
+        <v>2</v>
+      </c>
+      <c r="G104" s="10"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
@@ -3561,16 +3558,16 @@
       <c r="C105" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D105" s="12">
-        <v>64</v>
+      <c r="D105" s="11">
+        <v>36</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="F105" s="13">
-        <v>5</v>
-      </c>
-      <c r="G105" s="11"/>
+      <c r="F105" s="12">
+        <v>3</v>
+      </c>
+      <c r="G105" s="10"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
@@ -3582,16 +3579,16 @@
       <c r="C106" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D106" s="12">
-        <v>64</v>
+      <c r="D106" s="11">
+        <v>36</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F106" s="13">
-        <v>3</v>
-      </c>
-      <c r="G106" s="11"/>
+      <c r="F106" s="12">
+        <v>1</v>
+      </c>
+      <c r="G106" s="10"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
@@ -3603,16 +3600,16 @@
       <c r="C107" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D107" s="12">
-        <v>146</v>
+      <c r="D107" s="11">
+        <v>78</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F107" s="13">
-        <v>0</v>
-      </c>
-      <c r="G107" s="11"/>
+      <c r="F107" s="12">
+        <v>3</v>
+      </c>
+      <c r="G107" s="10"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
@@ -3624,16 +3621,16 @@
       <c r="C108" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D108" s="12">
-        <v>146</v>
+      <c r="D108" s="11">
+        <v>78</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="F108" s="13">
-        <v>7</v>
-      </c>
-      <c r="G108" s="11"/>
+      <c r="F108" s="12">
+        <v>2</v>
+      </c>
+      <c r="G108" s="10"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
@@ -3645,16 +3642,16 @@
       <c r="C109" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D109" s="12">
-        <v>146</v>
+      <c r="D109" s="11">
+        <v>150</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F109" s="13">
-        <v>1</v>
-      </c>
-      <c r="G109" s="11"/>
+      <c r="F109" s="12">
+        <v>2</v>
+      </c>
+      <c r="G109" s="10"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
@@ -3666,16 +3663,16 @@
       <c r="C110" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D110" s="12">
-        <v>20.5</v>
+      <c r="D110" s="11">
+        <v>150</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="F110" s="13">
-        <v>4</v>
-      </c>
-      <c r="G110" s="11"/>
+      <c r="F110" s="12">
+        <v>2</v>
+      </c>
+      <c r="G110" s="10"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
@@ -3687,16 +3684,16 @@
       <c r="C111" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D111" s="12">
-        <v>34.15</v>
+      <c r="D111" s="11">
+        <v>71</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="F111" s="13">
+      <c r="F111" s="12">
         <v>1</v>
       </c>
-      <c r="G111" s="11"/>
+      <c r="G111" s="10"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
@@ -3708,16 +3705,16 @@
       <c r="C112" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D112" s="12">
-        <v>34.15</v>
+      <c r="D112" s="11">
+        <v>35.5</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="F112" s="13">
-        <v>1</v>
-      </c>
-      <c r="G112" s="11"/>
+      <c r="F112" s="12">
+        <v>23</v>
+      </c>
+      <c r="G112" s="10"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
@@ -3729,31 +3726,31 @@
       <c r="C113" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D113" s="12">
-        <v>76.350000000000009</v>
+      <c r="D113" s="11">
+        <v>35.5</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="F113" s="13">
-        <v>2</v>
-      </c>
-      <c r="G113" s="11"/>
+      <c r="F113" s="12">
+        <v>0</v>
+      </c>
+      <c r="G113" s="10"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B114" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="D114" s="12">
-        <v>6.55</v>
+      <c r="D114" s="11">
+        <v>35.5</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="F114" s="13">
-        <v>0</v>
-      </c>
-      <c r="G114" s="11"/>
+      <c r="F114" s="12">
+        <v>4</v>
+      </c>
+      <c r="G114" s="10"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B115" s="9" t="s">
@@ -3762,16 +3759,16 @@
       <c r="C115" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D115" s="12">
-        <v>10</v>
+      <c r="D115" s="11">
+        <v>64</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F115" s="13">
-        <v>6</v>
-      </c>
-      <c r="G115" s="11"/>
+      <c r="F115" s="12">
+        <v>8</v>
+      </c>
+      <c r="G115" s="10"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B116" s="9" t="s">
@@ -3780,16 +3777,16 @@
       <c r="C116" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D116" s="12">
-        <v>8.5</v>
+      <c r="D116" s="11">
+        <v>64</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="F116" s="13">
-        <v>1</v>
-      </c>
-      <c r="G116" s="11"/>
+      <c r="F116" s="12">
+        <v>5</v>
+      </c>
+      <c r="G116" s="10"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B117" s="9" t="s">
@@ -3798,16 +3795,16 @@
       <c r="C117" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D117" s="12">
-        <v>10</v>
+      <c r="D117" s="11">
+        <v>146</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F117" s="13">
+      <c r="F117" s="12">
         <v>0</v>
       </c>
-      <c r="G117" s="11"/>
+      <c r="G117" s="10"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
@@ -3819,16 +3816,16 @@
       <c r="C118" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D118" s="12">
-        <v>46.35</v>
+      <c r="D118" s="11">
+        <v>146</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F118" s="13">
-        <v>3</v>
-      </c>
-      <c r="G118" s="11"/>
+      <c r="F118" s="12">
+        <v>7</v>
+      </c>
+      <c r="G118" s="10"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
@@ -3840,16 +3837,16 @@
       <c r="C119" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D119" s="12">
-        <v>46.35</v>
+      <c r="D119" s="11">
+        <v>146</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="F119" s="13">
-        <v>2</v>
-      </c>
-      <c r="G119" s="11"/>
+      <c r="F119" s="12">
+        <v>0</v>
+      </c>
+      <c r="G119" s="10"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
@@ -3861,16 +3858,16 @@
       <c r="C120" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D120" s="12">
-        <v>107.35000000000001</v>
+      <c r="D120" s="11">
+        <v>20.5</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F120" s="13">
-        <v>2</v>
-      </c>
-      <c r="G120" s="11"/>
+      <c r="F120" s="12">
+        <v>4</v>
+      </c>
+      <c r="G120" s="10"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
@@ -3882,16 +3879,16 @@
       <c r="C121" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D121" s="12">
-        <v>52</v>
+      <c r="D121" s="11">
+        <v>34.15</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F121" s="13">
-        <v>2</v>
-      </c>
-      <c r="G121" s="11"/>
+      <c r="F121" s="12">
+        <v>1</v>
+      </c>
+      <c r="G121" s="10"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
@@ -3903,16 +3900,16 @@
       <c r="C122" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D122" s="12">
-        <v>52</v>
+      <c r="D122" s="11">
+        <v>34.15</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="F122" s="13">
-        <v>0</v>
-      </c>
-      <c r="G122" s="11"/>
+      <c r="F122" s="12">
+        <v>1</v>
+      </c>
+      <c r="G122" s="10"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
@@ -3924,16 +3921,16 @@
       <c r="C123" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D123" s="12">
-        <v>55</v>
+      <c r="D123" s="11">
+        <v>76.350000000000009</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F123" s="13">
-        <v>3</v>
-      </c>
-      <c r="G123" s="11"/>
+      <c r="F123" s="12">
+        <v>2</v>
+      </c>
+      <c r="G123" s="10"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
@@ -3945,16 +3942,16 @@
       <c r="C124" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D124" s="12">
-        <v>95.990000000000009</v>
+      <c r="D124" s="11">
+        <v>6.55</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F124" s="13">
-        <v>2</v>
-      </c>
-      <c r="G124" s="11"/>
+      <c r="F124" s="12">
+        <v>0</v>
+      </c>
+      <c r="G124" s="10"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
@@ -3966,16 +3963,16 @@
       <c r="C125" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D125" s="12">
-        <v>114.49000000000001</v>
+      <c r="D125" s="11">
+        <v>10</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="F125" s="13">
-        <v>2</v>
-      </c>
-      <c r="G125" s="11"/>
+      <c r="F125" s="12">
+        <v>5</v>
+      </c>
+      <c r="G125" s="10"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
@@ -3987,16 +3984,16 @@
       <c r="C126" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D126" s="12">
-        <v>95.990000000000009</v>
+      <c r="D126" s="11">
+        <v>10</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="F126" s="13">
+      <c r="F126" s="12">
         <v>1</v>
       </c>
-      <c r="G126" s="11"/>
+      <c r="G126" s="10"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
@@ -4008,16 +4005,16 @@
       <c r="C127" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D127" s="12">
-        <v>225</v>
+      <c r="D127" s="11">
+        <v>10</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="F127" s="13">
-        <v>3</v>
-      </c>
-      <c r="G127" s="11"/>
+      <c r="F127" s="12">
+        <v>2</v>
+      </c>
+      <c r="G127" s="10"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
@@ -4029,16 +4026,16 @@
       <c r="C128" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D128" s="12">
-        <v>212</v>
+      <c r="D128" s="11">
+        <v>46.35</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F128" s="13">
+      <c r="F128" s="12">
         <v>3</v>
       </c>
-      <c r="G128" s="11"/>
+      <c r="G128" s="10"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
@@ -4050,16 +4047,16 @@
       <c r="C129" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D129" s="12">
-        <v>212</v>
+      <c r="D129" s="11">
+        <v>46.35</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F129" s="13">
-        <v>0</v>
-      </c>
-      <c r="G129" s="11"/>
+      <c r="F129" s="12">
+        <v>2</v>
+      </c>
+      <c r="G129" s="10"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B130" s="9" t="s">
@@ -4068,16 +4065,16 @@
       <c r="C130" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D130" s="12">
-        <v>40</v>
+      <c r="D130" s="11">
+        <v>107.35000000000001</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="F130" s="13">
+      <c r="F130" s="12">
         <v>2</v>
       </c>
-      <c r="G130" s="11"/>
+      <c r="G130" s="10"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B131" s="9" t="s">
@@ -4086,16 +4083,16 @@
       <c r="C131" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D131" s="12">
-        <v>86</v>
+      <c r="D131" s="11">
+        <v>52</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="F131" s="13">
-        <v>0</v>
-      </c>
-      <c r="G131" s="11"/>
+      <c r="F131" s="12">
+        <v>2</v>
+      </c>
+      <c r="G131" s="10"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B132" s="9" t="s">
@@ -4104,16 +4101,16 @@
       <c r="C132" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D132" s="12">
-        <v>108.31</v>
+      <c r="D132" s="11">
+        <v>52</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F132" s="13">
-        <v>1</v>
-      </c>
-      <c r="G132" s="11"/>
+      <c r="F132" s="12">
+        <v>0</v>
+      </c>
+      <c r="G132" s="10"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B133" s="9" t="s">
@@ -4122,16 +4119,16 @@
       <c r="C133" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D133" s="12">
-        <v>73.650000000000006</v>
+      <c r="D133" s="11">
+        <v>55</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="F133" s="13">
-        <v>2</v>
-      </c>
-      <c r="G133" s="11"/>
+      <c r="F133" s="12">
+        <v>3</v>
+      </c>
+      <c r="G133" s="10"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B134" s="9" t="s">
@@ -4140,16 +4137,16 @@
       <c r="C134" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D134" s="12">
-        <v>190</v>
+      <c r="D134" s="11">
+        <v>95.990000000000009</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F134" s="13">
-        <v>1</v>
-      </c>
-      <c r="G134" s="11"/>
+      <c r="F134" s="12">
+        <v>2</v>
+      </c>
+      <c r="G134" s="10"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B135" s="9" t="s">
@@ -4158,138 +4155,188 @@
       <c r="C135" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D135" s="12">
-        <v>67</v>
+      <c r="D135" s="11">
+        <v>114.49000000000001</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="F135" s="13">
+      <c r="F135" s="12">
+        <v>2</v>
+      </c>
+      <c r="G135" s="10"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D136" s="11">
+        <v>95.990000000000009</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" s="12">
         <v>1</v>
       </c>
-      <c r="G135" s="11"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E136" s="2"/>
-      <c r="F136" s="5"/>
       <c r="G136" s="10"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D137" s="11">
+        <v>225</v>
+      </c>
       <c r="E137" s="2"/>
-      <c r="F137" s="5"/>
+      <c r="F137" s="12">
+        <v>3</v>
+      </c>
       <c r="G137" s="10"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D138" s="11">
+        <v>212</v>
+      </c>
       <c r="E138" s="2"/>
-      <c r="F138" s="5"/>
+      <c r="F138" s="12">
+        <v>3</v>
+      </c>
       <c r="G138" s="10"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D139" s="11">
+        <v>212</v>
+      </c>
       <c r="E139" s="2"/>
-      <c r="F139" s="5"/>
+      <c r="F139" s="12">
+        <v>0</v>
+      </c>
       <c r="G139" s="10"/>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D140" s="11">
+        <v>40</v>
+      </c>
       <c r="E140" s="2"/>
-      <c r="F140" s="5"/>
+      <c r="F140" s="12">
+        <v>2</v>
+      </c>
       <c r="G140" s="10"/>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D141" s="11">
+        <v>86</v>
+      </c>
       <c r="E141" s="2"/>
-      <c r="F141" s="5"/>
+      <c r="F141" s="12">
+        <v>0</v>
+      </c>
       <c r="G141" s="10"/>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D142" s="11">
+        <v>108.31</v>
+      </c>
       <c r="E142" s="2"/>
-      <c r="F142" s="5"/>
+      <c r="F142" s="12">
+        <v>1</v>
+      </c>
       <c r="G142" s="10"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D143" s="11">
+        <v>73.650000000000006</v>
+      </c>
       <c r="E143" s="2"/>
-      <c r="F143" s="5"/>
+      <c r="F143" s="12">
+        <v>2</v>
+      </c>
       <c r="G143" s="10"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D144" s="11">
+        <v>190</v>
+      </c>
       <c r="E144" s="2"/>
-      <c r="F144" s="5"/>
+      <c r="F144" s="12">
+        <v>1</v>
+      </c>
       <c r="G144" s="10"/>
     </row>
-    <row r="145" spans="5:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D145" s="11">
+        <v>67</v>
+      </c>
       <c r="E145" s="2"/>
-      <c r="F145" s="5"/>
+      <c r="F145" s="12">
+        <v>0</v>
+      </c>
       <c r="G145" s="10"/>
     </row>
-    <row r="146" spans="5:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E146" s="2"/>
       <c r="F146" s="5"/>
       <c r="G146" s="10"/>
     </row>
-    <row r="147" spans="5:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E147" s="2"/>
       <c r="F147" s="5"/>
       <c r="G147" s="10"/>
     </row>
-    <row r="148" spans="5:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E148" s="2"/>
       <c r="F148" s="5"/>
       <c r="G148" s="10"/>
     </row>
-    <row r="149" spans="5:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E149" s="2"/>
       <c r="F149" s="5"/>
       <c r="G149" s="10"/>
     </row>
-    <row r="150" spans="5:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E150" s="2"/>
       <c r="F150" s="5"/>
       <c r="G150" s="10"/>
     </row>
-    <row r="151" spans="5:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E151" s="2"/>
       <c r="F151" s="5"/>
       <c r="G151" s="10"/>
     </row>
-    <row r="152" spans="5:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E152" s="2"/>
       <c r="F152" s="5"/>
       <c r="G152" s="10"/>
     </row>
-    <row r="153" spans="5:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E153" s="2"/>
       <c r="F153" s="5"/>
       <c r="G153" s="10"/>
     </row>
-    <row r="154" spans="5:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E154" s="2"/>
       <c r="F154" s="5"/>
       <c r="G154" s="10"/>
     </row>
-    <row r="155" spans="5:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E155" s="2"/>
       <c r="F155" s="5"/>
       <c r="G155" s="10"/>
     </row>
-    <row r="156" spans="5:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E156" s="2"/>
       <c r="F156" s="5"/>
       <c r="G156" s="10"/>
     </row>
-    <row r="157" spans="5:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E157" s="2"/>
       <c r="F157" s="5"/>
       <c r="G157" s="10"/>
     </row>
-    <row r="158" spans="5:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E158" s="2"/>
       <c r="F158" s="5"/>
       <c r="G158" s="10"/>
     </row>
-    <row r="159" spans="5:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E159" s="2"/>
       <c r="F159" s="5"/>
       <c r="G159" s="10"/>
     </row>
-    <row r="160" spans="5:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E160" s="2"/>
       <c r="F160" s="5"/>
       <c r="G160" s="10"/>
